--- a/Grondwatermonitoringput (GMW)/BROObject - GMW IMBRO datafile NL (v1.x).xlsx
+++ b/Grondwatermonitoringput (GMW)/BROObject - GMW IMBRO datafile NL (v1.x).xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1678,15 +1678,15 @@
     <tabColor theme="3" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" customWidth="1"/>
+    <col min="2" max="2" width="50.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1792,7 +1792,7 @@
       <c r="I6" s="40"/>
       <c r="J6" s="40"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1">
+    <row r="7" spans="1:10" ht="15" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -1808,7 +1808,7 @@
       <c r="I7" s="40"/>
       <c r="J7" s="40"/>
     </row>
-    <row r="9" spans="1:10" ht="23.25">
+    <row r="9" spans="1:10" ht="23.4">
       <c r="A9" s="42" t="s">
         <v>201</v>
       </c>
@@ -1843,16 +1843,16 @@
         <v>207</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="10.15" customHeight="1">
+    <row r="16" spans="1:10" ht="10.199999999999999" customHeight="1">
       <c r="A16" s="43"/>
     </row>
-    <row r="17" spans="1:1" ht="23.25">
+    <row r="17" spans="1:1" ht="23.4">
       <c r="A17" s="42" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="7.9" customHeight="1"/>
-    <row r="33" spans="1:1" ht="23.25">
+    <row r="32" spans="1:1" ht="7.95" customHeight="1"/>
+    <row r="33" spans="1:1" ht="23.4">
       <c r="A33" s="42" t="s">
         <v>209</v>
       </c>
@@ -1873,25 +1873,25 @@
     <tabColor rgb="FF005E6A"/>
   </sheetPr>
   <dimension ref="A1:S11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
     <col min="3" max="5" width="24" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.6640625" customWidth="1"/>
     <col min="18" max="18" width="15" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -1986,7 +1986,7 @@
       <c r="G6" s="15"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" spans="1:19" ht="15.75" thickBot="1">
+    <row r="7" spans="1:19" ht="15" thickBot="1">
       <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
@@ -2000,7 +2000,7 @@
       <c r="G7" s="7"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1">
+    <row r="8" spans="1:19" ht="15" thickBot="1">
       <c r="A8" s="15"/>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -2128,7 +2128,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15.75" thickBot="1">
+    <row r="11" spans="1:19" ht="15" thickBot="1">
       <c r="A11" s="6">
         <v>1</v>
       </c>
@@ -2250,26 +2250,26 @@
     <tabColor rgb="FF005E6A"/>
   </sheetPr>
   <dimension ref="A1:S3"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.88671875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="23.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="37" customFormat="1">
@@ -2331,7 +2331,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="19.149999999999999" customHeight="1">
+    <row r="2" spans="1:19" ht="19.2" customHeight="1">
       <c r="A2" s="11" t="s">
         <v>11</v>
       </c>
@@ -2516,29 +2516,29 @@
     <tabColor rgb="FF005E6A"/>
   </sheetPr>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="33" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2671,7 +2671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="15.75" thickBot="1">
+    <row r="3" spans="1:21" ht="15" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -2773,15 +2773,15 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -2807,7 +2807,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.149999999999999" customHeight="1">
+    <row r="2" spans="1:7" ht="19.2" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>11</v>
       </c>
@@ -2876,28 +2876,28 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="24" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="28.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="24" customFormat="1" ht="15.75" thickBot="1">
+    <row r="1" spans="1:17" s="24" customFormat="1" ht="15" thickBot="1">
       <c r="A1" s="25" t="s">
         <v>23</v>
       </c>
